--- a/Documents/Faculty_Sheet/Faculty_Roster.xlsx
+++ b/Documents/Faculty_Sheet/Faculty_Roster.xlsx
@@ -423,14 +423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +460,222 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dr. Liwayway Bautista</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>liwayway.bautista@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Learning analytics, online learning, and student engagement in graduate education</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dr. Marlon Geronimo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>marlon.geronimo@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Machine learning, educational data analytics, and predicting student performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dr. Patricia Salvador</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>patricia.salvador@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Online learning, learning management systems, education technology, and curriculum development</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dr. Teodoro Ramos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>teodoro.ramos@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Learning analytics, online learning assessment, and educational data science</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dr. Adriana Santos</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>adriana.santos@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Health informatics, public health, and medical systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dr. Benjamin Reyes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>benjamin.reyes@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Finance, business analytics, accounting, and financial technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dr. Celeste Tan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>celeste.tan@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Psychology, student well-being, and behavioral research</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dr. Daniel Uy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Adviser / Panel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>daniel.uy@usls.edu.ph</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Engineering systems, automation, data modeling, and predictive analytics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
